--- a/r4-ELGA-IV-Herzinsuffizienz-fokuswoche/ValueSet-acetherapy.xlsx
+++ b/r4-ELGA-IV-Herzinsuffizienz-fokuswoche/ValueSet-acetherapy.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-13T12:12:25+00:00</t>
+    <t>2024-12-13T12:39:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-IV-Herzinsuffizienz-fokuswoche/ValueSet-acetherapy.xlsx
+++ b/r4-ELGA-IV-Herzinsuffizienz-fokuswoche/ValueSet-acetherapy.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-13T12:39:58+00:00</t>
+    <t>2024-12-17T14:24:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-IV-Herzinsuffizienz-fokuswoche/ValueSet-acetherapy.xlsx
+++ b/r4-ELGA-IV-Herzinsuffizienz-fokuswoche/ValueSet-acetherapy.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-17T14:24:59+00:00</t>
+    <t>2024-12-18T11:56:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-IV-Herzinsuffizienz-fokuswoche/ValueSet-acetherapy.xlsx
+++ b/r4-ELGA-IV-Herzinsuffizienz-fokuswoche/ValueSet-acetherapy.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-18T11:56:12+00:00</t>
+    <t>2024-12-18T12:33:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-IV-Herzinsuffizienz-fokuswoche/ValueSet-acetherapy.xlsx
+++ b/r4-ELGA-IV-Herzinsuffizienz-fokuswoche/ValueSet-acetherapy.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-18T12:33:25+00:00</t>
+    <t>2025-01-08T07:19:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-IV-Herzinsuffizienz-fokuswoche/ValueSet-acetherapy.xlsx
+++ b/r4-ELGA-IV-Herzinsuffizienz-fokuswoche/ValueSet-acetherapy.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-08T07:19:57+00:00</t>
+    <t>2025-01-08T14:21:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-IV-Herzinsuffizienz-fokuswoche/ValueSet-acetherapy.xlsx
+++ b/r4-ELGA-IV-Herzinsuffizienz-fokuswoche/ValueSet-acetherapy.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-08T14:21:56+00:00</t>
+    <t>2025-01-08T14:42:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-IV-Herzinsuffizienz-fokuswoche/ValueSet-acetherapy.xlsx
+++ b/r4-ELGA-IV-Herzinsuffizienz-fokuswoche/ValueSet-acetherapy.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-08T14:42:30+00:00</t>
+    <t>2025-01-08T14:46:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-IV-Herzinsuffizienz-fokuswoche/ValueSet-acetherapy.xlsx
+++ b/r4-ELGA-IV-Herzinsuffizienz-fokuswoche/ValueSet-acetherapy.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-08T14:46:01+00:00</t>
+    <t>2025-01-08T14:48:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-IV-Herzinsuffizienz-fokuswoche/ValueSet-acetherapy.xlsx
+++ b/r4-ELGA-IV-Herzinsuffizienz-fokuswoche/ValueSet-acetherapy.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-08T14:48:43+00:00</t>
+    <t>2025-01-13T13:05:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-IV-Herzinsuffizienz-fokuswoche/ValueSet-acetherapy.xlsx
+++ b/r4-ELGA-IV-Herzinsuffizienz-fokuswoche/ValueSet-acetherapy.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T13:05:07+00:00</t>
+    <t>2025-01-16T07:14:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-IV-Herzinsuffizienz-fokuswoche/ValueSet-acetherapy.xlsx
+++ b/r4-ELGA-IV-Herzinsuffizienz-fokuswoche/ValueSet-acetherapy.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-16T07:14:22+00:00</t>
+    <t>2025-01-20T09:51:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-IV-Herzinsuffizienz-fokuswoche/ValueSet-acetherapy.xlsx
+++ b/r4-ELGA-IV-Herzinsuffizienz-fokuswoche/ValueSet-acetherapy.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-20T09:51:26+00:00</t>
+    <t>2025-01-20T10:29:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-IV-Herzinsuffizienz-fokuswoche/ValueSet-acetherapy.xlsx
+++ b/r4-ELGA-IV-Herzinsuffizienz-fokuswoche/ValueSet-acetherapy.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-20T10:29:28+00:00</t>
+    <t>2025-01-21T15:51:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-IV-Herzinsuffizienz-fokuswoche/ValueSet-acetherapy.xlsx
+++ b/r4-ELGA-IV-Herzinsuffizienz-fokuswoche/ValueSet-acetherapy.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-21T15:51:25+00:00</t>
+    <t>2025-01-22T12:30:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-IV-Herzinsuffizienz-fokuswoche/ValueSet-acetherapy.xlsx
+++ b/r4-ELGA-IV-Herzinsuffizienz-fokuswoche/ValueSet-acetherapy.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-22T12:30:38+00:00</t>
+    <t>2025-01-23T11:55:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-IV-Herzinsuffizienz-fokuswoche/ValueSet-acetherapy.xlsx
+++ b/r4-ELGA-IV-Herzinsuffizienz-fokuswoche/ValueSet-acetherapy.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-23T11:55:38+00:00</t>
+    <t>2025-01-29T11:32:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
